--- a/fixtures/formula_gauntlet.xlsx
+++ b/fixtures/formula_gauntlet.xlsx
@@ -490,10 +490,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C3">
-        <f>COUNTIF('Math'!$E$2:$E$58,"OK")</f>
+        <f>COUNTIF('Math'!$E$2:$E$62,"OK")</f>
         <v/>
       </c>
       <c r="D3">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C4">
-        <f>COUNTIF('Text'!$E$2:$E$34,"OK")</f>
+        <f>COUNTIF('Text'!$E$2:$E$56,"OK")</f>
         <v/>
       </c>
       <c r="D4">
@@ -544,10 +544,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C6">
-        <f>COUNTIF('Lookup'!$E$2:$E$32,"OK")</f>
+        <f>COUNTIF('Lookup'!$E$2:$E$41,"OK")</f>
         <v/>
       </c>
       <c r="D6">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C8">
-        <f>COUNTIF('Stats'!$E$2:$E$24,"OK")</f>
+        <f>COUNTIF('Stats'!$E$2:$E$28,"OK")</f>
         <v/>
       </c>
       <c r="D8">
@@ -688,10 +688,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C14">
-        <f>COUNTIF('Gaps'!$E$2:$E$9,"OK")</f>
+        <f>COUNTIF('Gaps'!$E$2:$E$5,"OK")</f>
         <v/>
       </c>
       <c r="D14">
@@ -2252,7 +2252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2297,15 +2297,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>no SUMPRODUCT</t>
+          <t>no native TRANSPOSE (MY* only)</t>
         </is>
       </c>
       <c r="C2">
-        <f>SUMPRODUCT(Data!B2:B6,Data!C2:C6)</f>
+        <f>SUM(TRANSPOSE(Data!E1:E8))</f>
         <v/>
       </c>
       <c r="D2" t="n">
-        <v>149.5</v>
+        <v>39</v>
       </c>
       <c r="E2">
         <f>IF(ISNUMBER(C2),IF(ABS(C2-D2)&lt;0.000000001,"OK","FAIL"),"FAIL")</f>
@@ -2320,20 +2320,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no ADDRESS</t>
+          <t>no SEQUENCE</t>
         </is>
       </c>
       <c r="C3">
-        <f>ADDRESS(1,1)</f>
-        <v/>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>$A$1</t>
-        </is>
+        <f>SUM(SEQUENCE(3))</f>
+        <v/>
+      </c>
+      <c r="D3" t="n">
+        <v>6</v>
       </c>
       <c r="E3">
-        <f>IF(ISTEXT(C3),IF(EXACT(C3,D3),"OK","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(C3),IF(ABS(C3-D3)&lt;0.000000001,"OK","FAIL"),"FAIL")</f>
         <v/>
       </c>
     </row>
@@ -2345,20 +2343,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>no PROPER</t>
+          <t>no LET</t>
         </is>
       </c>
       <c r="C4">
-        <f>PROPER("hello world")</f>
-        <v/>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Hello World</t>
-        </is>
+        <f>LET(x,2,x*3)</f>
+        <v/>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
       </c>
       <c r="E4">
-        <f>IF(ISTEXT(C4),IF(EXACT(C4,D4),"OK","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(C4),IF(ABS(C4-D4)&lt;0.000000001,"OK","FAIL"),"FAIL")</f>
         <v/>
       </c>
     </row>
@@ -2370,114 +2366,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no CODE (UNICODE exists)</t>
+          <t>no TEXTSPLIT (anchor cell)</t>
         </is>
       </c>
       <c r="C5">
-        <f>CODE("A")</f>
-        <v/>
-      </c>
-      <c r="D5" t="n">
-        <v>65</v>
+        <f>TEXTSPLIT("a,b",",")</f>
+        <v/>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
       </c>
       <c r="E5">
-        <f>IF(ISNUMBER(C5),IF(ABS(C5-D5)&lt;0.000000001,"OK","FAIL"),"FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>GAP005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>no MODE</t>
-        </is>
-      </c>
-      <c r="C6">
-        <f>MODE(1,2,2,3)</f>
-        <v/>
-      </c>
-      <c r="D6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <f>IF(ISNUMBER(C6),IF(ABS(C6-D6)&lt;0.000000001,"OK","FAIL"),"FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>GAP006</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>no REPLACE</t>
-        </is>
-      </c>
-      <c r="C7">
-        <f>REPLACE("abcdef",2,3,"XY")</f>
-        <v/>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>aXYef</t>
-        </is>
-      </c>
-      <c r="E7">
-        <f>IF(ISTEXT(C7),IF(EXACT(C7,D7),"OK","FAIL"),"FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>GAP007</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>no NUMBERVALUE</t>
-        </is>
-      </c>
-      <c r="C8">
-        <f>NUMBERVALUE("1.5")</f>
-        <v/>
-      </c>
-      <c r="D8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E8">
-        <f>IF(ISNUMBER(C8),IF(ABS(C8-D8)&lt;0.000000001,"OK","FAIL"),"FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>GAP008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>no FIXED</t>
-        </is>
-      </c>
-      <c r="C9">
-        <f>FIXED(1234.567,1)</f>
-        <v/>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>1,234.6</t>
-        </is>
-      </c>
-      <c r="E9">
-        <f>IF(ISTEXT(C9),IF(EXACT(C9,D9),"OK","FAIL"),"FAIL")</f>
+        <f>IF(ISTEXT(C5),IF(EXACT(C5,D5),"OK","FAIL"),"FAIL")</f>
         <v/>
       </c>
     </row>
@@ -3496,7 +3398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4600,16 +4502,14 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55">
-        <f>ROMAN(1990)</f>
-        <v/>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>MCMXC</t>
-        </is>
+        <f>SUMPRODUCT(Data!B2:B6,Data!C2:C6)</f>
+        <v/>
+      </c>
+      <c r="D55" t="n">
+        <v>149.5</v>
       </c>
       <c r="E55">
-        <f>IF(ISTEXT(C55),IF(EXACT(C55,D55),"OK","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(C55),IF(ABS(C55-D55)&lt;0.000000001,"OK","FAIL"),"FAIL")</f>
         <v/>
       </c>
     </row>
@@ -4619,13 +4519,17 @@
           <t>MAT055</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>single array just sums</t>
+        </is>
+      </c>
       <c r="C56">
-        <f>ARABIC("XIV")</f>
+        <f>SUMPRODUCT(Data!E1:E8)</f>
         <v/>
       </c>
       <c r="D56" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="E56">
         <f>IF(ISNUMBER(C56),IF(ABS(C56-D56)&lt;0.000000001,"OK","FAIL"),"FAIL")</f>
@@ -4638,18 +4542,20 @@
           <t>MAT056</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>text elements count as 0</t>
+        </is>
+      </c>
       <c r="C57">
-        <f>BASE(255,16)</f>
-        <v/>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>FF</t>
-        </is>
+        <f>SUMPRODUCT(Data!A2:A6,Data!B2:B6)</f>
+        <v/>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
       </c>
       <c r="E57">
-        <f>IF(ISTEXT(C57),IF(EXACT(C57,D57),"OK","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(C57),IF(ABS(C57-D57)&lt;0.000000001,"OK","FAIL"),"FAIL")</f>
         <v/>
       </c>
     </row>
@@ -4659,16 +4565,100 @@
           <t>MAT057</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>dimension mismatch</t>
+        </is>
+      </c>
       <c r="C58">
+        <f>SUMPRODUCT(Data!B2:B6,Data!C2:C5)</f>
+        <v/>
+      </c>
+      <c r="D58" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E58">
+        <f>IF(IFERROR(ERROR.TYPE(C58),0)=3,"OK","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>MAT058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59">
+        <f>ROMAN(1990)</f>
+        <v/>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>MCMXC</t>
+        </is>
+      </c>
+      <c r="E59">
+        <f>IF(ISTEXT(C59),IF(EXACT(C59,D59),"OK","FAIL"),"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>MAT059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60">
+        <f>ARABIC("XIV")</f>
+        <v/>
+      </c>
+      <c r="D60" t="n">
+        <v>14</v>
+      </c>
+      <c r="E60">
+        <f>IF(ISNUMBER(C60),IF(ABS(C60-D60)&lt;0.000000001,"OK","FAIL"),"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>MAT060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61">
+        <f>BASE(255,16)</f>
+        <v/>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>FF</t>
+        </is>
+      </c>
+      <c r="E61">
+        <f>IF(ISTEXT(C61),IF(EXACT(C61,D61),"OK","FAIL"),"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>MAT061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62">
         <f>DECIMAL("FF",16)</f>
         <v/>
       </c>
-      <c r="D58" t="n">
+      <c r="D62" t="n">
         <v>255</v>
       </c>
-      <c r="E58">
-        <f>IF(ISNUMBER(C58),IF(ABS(C58-D58)&lt;0.000000001,"OK","FAIL"),"FAIL")</f>
+      <c r="E62">
+        <f>IF(ISNUMBER(C62),IF(ABS(C62-D62)&lt;0.000000001,"OK","FAIL"),"FAIL")</f>
         <v/>
       </c>
     </row>
@@ -4683,7 +4673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5419,6 +5409,504 @@
       </c>
       <c r="E34">
         <f>IF(ISTEXT(C34),IF(EXACT(C34,D34),"OK","FAIL"),"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TEX034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35">
+        <f>PROPER("hello world")</f>
+        <v/>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Hello World</t>
+        </is>
+      </c>
+      <c r="E35">
+        <f>IF(ISTEXT(C35),IF(EXACT(C35,D35),"OK","FAIL"),"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TEX035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>any non-letter is a word break</t>
+        </is>
+      </c>
+      <c r="C36">
+        <f>PROPER("2-cent's worth")</f>
+        <v/>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2-Cent'S Worth</t>
+        </is>
+      </c>
+      <c r="E36">
+        <f>IF(ISTEXT(C36),IF(EXACT(C36,D36),"OK","FAIL"),"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>TEX036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37">
+        <f>PROPER(Data!H3)</f>
+        <v/>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Mixed Case</t>
+        </is>
+      </c>
+      <c r="E37">
+        <f>IF(ISTEXT(C37),IF(EXACT(C37,D37),"OK","FAIL"),"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TEX037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38">
+        <f>CODE("A")</f>
+        <v/>
+      </c>
+      <c r="D38" t="n">
+        <v>65</v>
+      </c>
+      <c r="E38">
+        <f>IF(ISNUMBER(C38),IF(ABS(C38-D38)&lt;0.000000001,"OK","FAIL"),"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>TEX038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Win-1252 C1 range</t>
+        </is>
+      </c>
+      <c r="C39">
+        <f>CODE("€")</f>
+        <v/>
+      </c>
+      <c r="D39" t="n">
+        <v>128</v>
+      </c>
+      <c r="E39">
+        <f>IF(ISNUMBER(C39),IF(ABS(C39-D39)&lt;0.000000001,"OK","FAIL"),"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TEX039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>round-trip</t>
+        </is>
+      </c>
+      <c r="C40">
+        <f>CHAR(CODE("a"))</f>
+        <v/>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E40">
+        <f>IF(ISTEXT(C40),IF(EXACT(C40,D40),"OK","FAIL"),"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TEX040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>empty text</t>
+        </is>
+      </c>
+      <c r="C41">
+        <f>CODE("")</f>
+        <v/>
+      </c>
+      <c r="D41" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E41">
+        <f>IF(IFERROR(ERROR.TYPE(C41),0)=3,"OK","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TEX041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42">
+        <f>REPLACE("abcdef",2,3,"XY")</f>
+        <v/>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>aXYef</t>
+        </is>
+      </c>
+      <c r="E42">
+        <f>IF(ISTEXT(C42),IF(EXACT(C42,D42),"OK","FAIL"),"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>TEX042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>start past end appends</t>
+        </is>
+      </c>
+      <c r="C43">
+        <f>REPLACE("abc",9,2,"Z")</f>
+        <v/>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>abcZ</t>
+        </is>
+      </c>
+      <c r="E43">
+        <f>IF(ISTEXT(C43),IF(EXACT(C43,D43),"OK","FAIL"),"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>TEX043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>zero chars inserts</t>
+        </is>
+      </c>
+      <c r="C44">
+        <f>REPLACE("abc",1,0,"Z")</f>
+        <v/>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Zabc</t>
+        </is>
+      </c>
+      <c r="E44">
+        <f>IF(ISTEXT(C44),IF(EXACT(C44,D44),"OK","FAIL"),"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>TEX044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>start below 1</t>
+        </is>
+      </c>
+      <c r="C45">
+        <f>REPLACE("abc",0,1,"Z")</f>
+        <v/>
+      </c>
+      <c r="D45" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E45">
+        <f>IF(IFERROR(ERROR.TYPE(C45),0)=3,"OK","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>TEX045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46">
+        <f>FIXED(1234.567,1)</f>
+        <v/>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1,234.6</t>
+        </is>
+      </c>
+      <c r="E46">
+        <f>IF(ISTEXT(C46),IF(EXACT(C46,D46),"OK","FAIL"),"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>TEX046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>default 2 decimals</t>
+        </is>
+      </c>
+      <c r="C47">
+        <f>FIXED(1234.567)</f>
+        <v/>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1,234.57</t>
+        </is>
+      </c>
+      <c r="E47">
+        <f>IF(ISTEXT(C47),IF(EXACT(C47,D47),"OK","FAIL"),"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>TEX047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48">
+        <f>FIXED(-1234.567,1)</f>
+        <v/>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>-1,234.6</t>
+        </is>
+      </c>
+      <c r="E48">
+        <f>IF(ISTEXT(C48),IF(EXACT(C48,D48),"OK","FAIL"),"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>TEX048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>negative decimals round left</t>
+        </is>
+      </c>
+      <c r="C49">
+        <f>FIXED(1234.567,-2)</f>
+        <v/>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1,200</t>
+        </is>
+      </c>
+      <c r="E49">
+        <f>IF(ISTEXT(C49),IF(EXACT(C49,D49),"OK","FAIL"),"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>TEX049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>no_commas</t>
+        </is>
+      </c>
+      <c r="C50">
+        <f>FIXED(1234.567,1,TRUE)</f>
+        <v/>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1234.6</t>
+        </is>
+      </c>
+      <c r="E50">
+        <f>IF(ISTEXT(C50),IF(EXACT(C50,D50),"OK","FAIL"),"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>TEX050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51">
+        <f>NUMBERVALUE("1.5")</f>
+        <v/>
+      </c>
+      <c r="D51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E51">
+        <f>IF(ISNUMBER(C51),IF(ABS(C51-D51)&lt;0.000000001,"OK","FAIL"),"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>TEX051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>trailing percent divides</t>
+        </is>
+      </c>
+      <c r="C52">
+        <f>NUMBERVALUE("2.5%")</f>
+        <v/>
+      </c>
+      <c r="D52" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="E52">
+        <f>IF(ISNUMBER(C52),IF(ABS(C52-D52)&lt;0.000000001,"OK","FAIL"),"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>TEX052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>custom separators</t>
+        </is>
+      </c>
+      <c r="C53">
+        <f>NUMBERVALUE("3,50",",",".")</f>
+        <v/>
+      </c>
+      <c r="D53" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E53">
+        <f>IF(ISNUMBER(C53),IF(ABS(C53-D53)&lt;0.000000001,"OK","FAIL"),"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>TEX053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>group separators stripped</t>
+        </is>
+      </c>
+      <c r="C54">
+        <f>NUMBERVALUE("1,234.5")</f>
+        <v/>
+      </c>
+      <c r="D54" t="n">
+        <v>1234.5</v>
+      </c>
+      <c r="E54">
+        <f>IF(ISNUMBER(C54),IF(ABS(C54-D54)&lt;0.000000001,"OK","FAIL"),"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>TEX054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>empty text is zero</t>
+        </is>
+      </c>
+      <c r="C55">
+        <f>NUMBERVALUE("")</f>
+        <v/>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <f>IF(ISNUMBER(C55),IF(ABS(C55-D55)&lt;0.000000001,"OK","FAIL"),"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>TEX055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56">
+        <f>NUMBERVALUE("abc")</f>
+        <v/>
+      </c>
+      <c r="D56" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E56">
+        <f>IF(IFERROR(ERROR.TYPE(C56),0)=3,"OK","FAIL")</f>
         <v/>
       </c>
     </row>
@@ -5890,7 +6378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6571,6 +7059,225 @@
       </c>
       <c r="E32">
         <f>IF(ISNUMBER(C32),IF(ABS(C32-D32)&lt;0.000000001,"OK","FAIL"),"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>LOO032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33">
+        <f>ADDRESS(1,1)</f>
+        <v/>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>$A$1</t>
+        </is>
+      </c>
+      <c r="E33">
+        <f>IF(ISTEXT(C33),IF(EXACT(C33,D33),"OK","FAIL"),"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>LOO033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>row absolute</t>
+        </is>
+      </c>
+      <c r="C34">
+        <f>ADDRESS(2,3,2)</f>
+        <v/>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>C$2</t>
+        </is>
+      </c>
+      <c r="E34">
+        <f>IF(ISTEXT(C34),IF(EXACT(C34,D34),"OK","FAIL"),"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>LOO034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>column absolute</t>
+        </is>
+      </c>
+      <c r="C35">
+        <f>ADDRESS(2,3,3)</f>
+        <v/>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>$C2</t>
+        </is>
+      </c>
+      <c r="E35">
+        <f>IF(ISTEXT(C35),IF(EXACT(C35,D35),"OK","FAIL"),"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>LOO035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>relative</t>
+        </is>
+      </c>
+      <c r="C36">
+        <f>ADDRESS(2,3,4)</f>
+        <v/>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="E36">
+        <f>IF(ISTEXT(C36),IF(EXACT(C36,D36),"OK","FAIL"),"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>LOO036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>R1C1 absolute</t>
+        </is>
+      </c>
+      <c r="C37">
+        <f>ADDRESS(2,3,1,FALSE)</f>
+        <v/>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>R2C3</t>
+        </is>
+      </c>
+      <c r="E37">
+        <f>IF(ISTEXT(C37),IF(EXACT(C37,D37),"OK","FAIL"),"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>LOO037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>R1C1 relative</t>
+        </is>
+      </c>
+      <c r="C38">
+        <f>ADDRESS(2,3,4,FALSE)</f>
+        <v/>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>R[2]C[3]</t>
+        </is>
+      </c>
+      <c r="E38">
+        <f>IF(ISTEXT(C38),IF(EXACT(C38,D38),"OK","FAIL"),"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>LOO038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>sheet prefix</t>
+        </is>
+      </c>
+      <c r="C39">
+        <f>ADDRESS(1,1,1,TRUE,"Data")</f>
+        <v/>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Data!$A$1</t>
+        </is>
+      </c>
+      <c r="E39">
+        <f>IF(ISTEXT(C39),IF(EXACT(C39,D39),"OK","FAIL"),"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>LOO039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>quoted sheet</t>
+        </is>
+      </c>
+      <c r="C40">
+        <f>ADDRESS(1,1,1,TRUE,"My Sheet")</f>
+        <v/>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>'My Sheet'!$A$1</t>
+        </is>
+      </c>
+      <c r="E40">
+        <f>IF(ISTEXT(C40),IF(EXACT(C40,D40),"OK","FAIL"),"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>LOO040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>beyond last column</t>
+        </is>
+      </c>
+      <c r="C41">
+        <f>ADDRESS(1,16385)</f>
+        <v/>
+      </c>
+      <c r="D41" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E41">
+        <f>IF(IFERROR(ERROR.TYPE(C41),0)=3,"OK","FAIL")</f>
         <v/>
       </c>
     </row>
@@ -7221,7 +7928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7723,6 +8430,94 @@
         <v/>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>STA024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25">
+        <f>MODE(1,2,2,3)</f>
+        <v/>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25">
+        <f>IF(ISNUMBER(C25),IF(ABS(C25-D25)&lt;0.000000001,"OK","FAIL"),"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>STA025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>tie goes to first seen</t>
+        </is>
+      </c>
+      <c r="C26">
+        <f>MODE(3,3,2,2)</f>
+        <v/>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26">
+        <f>IF(ISNUMBER(C26),IF(ABS(C26-D26)&lt;0.000000001,"OK","FAIL"),"FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>STA026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>no repeats</t>
+        </is>
+      </c>
+      <c r="C27">
+        <f>MODE(1,2,3)</f>
+        <v/>
+      </c>
+      <c r="D27" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E27">
+        <f>IF(IFERROR(ERROR.TYPE(C27),0)=7,"OK","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>STA027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>all distinct</t>
+        </is>
+      </c>
+      <c r="C28">
+        <f>MODE(Data!E1:E8)</f>
+        <v/>
+      </c>
+      <c r="D28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E28">
+        <f>IF(IFERROR(ERROR.TYPE(C28),0)=7,"OK","FAIL")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
